--- a/grupos/3ASV - Estadisticos 20231.xlsx
+++ b/grupos/3ASV - Estadisticos 20231.xlsx
@@ -122,7 +122,7 @@
     <t>PEREZ ISLAS ANA LAURA</t>
   </si>
   <si>
-    <t>PUGA CABRERA  ALEJANDRO</t>
+    <t>PUGA CABRERA ALEJANDRO</t>
   </si>
   <si>
     <t>QUESADA OLGUIN JARED DE JESUS</t>
@@ -744,19 +744,19 @@
         <v>7</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J4">
         <v>-1</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M4">
         <v>-1</v>
@@ -780,10 +780,10 @@
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V4">
         <v>8</v>
@@ -792,7 +792,7 @@
         <v>8</v>
       </c>
       <c r="X4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y4">
         <v>7</v>
@@ -821,19 +821,19 @@
         <v>5</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J5">
         <v>-1</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M5">
         <v>-1</v>
@@ -857,7 +857,7 @@
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U5">
         <v>8</v>
@@ -898,19 +898,19 @@
         <v>8</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J6">
         <v>-1</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M6">
         <v>-1</v>
@@ -934,19 +934,19 @@
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V6">
         <v>9</v>
       </c>
       <c r="W6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y6">
         <v>8</v>
@@ -975,19 +975,19 @@
         <v>10</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J7">
         <v>-1</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M7">
         <v>-1</v>
@@ -1011,7 +1011,7 @@
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U7">
         <v>9</v>
@@ -1023,7 +1023,7 @@
         <v>8</v>
       </c>
       <c r="X7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y7">
         <v>10</v>
@@ -1052,19 +1052,19 @@
         <v>8</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J8">
         <v>-1</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M8">
         <v>-1</v>
@@ -1097,10 +1097,10 @@
         <v>7</v>
       </c>
       <c r="W8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y8">
         <v>8</v>
@@ -1129,19 +1129,19 @@
         <v>9</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J9">
         <v>-1</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M9">
         <v>-1</v>
@@ -1174,10 +1174,10 @@
         <v>8</v>
       </c>
       <c r="W9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y9">
         <v>9</v>
@@ -1206,19 +1206,19 @@
         <v>10</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J10">
         <v>-1</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M10">
         <v>-1</v>
@@ -1242,10 +1242,10 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V10">
         <v>8</v>
@@ -1254,7 +1254,7 @@
         <v>8</v>
       </c>
       <c r="X10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y10">
         <v>10</v>
@@ -1283,19 +1283,19 @@
         <v>8</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J11">
         <v>-1</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M11">
         <v>-1</v>
@@ -1319,7 +1319,7 @@
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U11">
         <v>9</v>
@@ -1328,7 +1328,7 @@
         <v>9</v>
       </c>
       <c r="W11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X11">
         <v>10</v>
@@ -1360,19 +1360,19 @@
         <v>5</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J12">
         <v>-1</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M12">
         <v>-1</v>
@@ -1396,7 +1396,7 @@
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U12">
         <v>9</v>
@@ -1405,10 +1405,10 @@
         <v>7</v>
       </c>
       <c r="W12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X12">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y12">
         <v>5</v>
@@ -1437,19 +1437,19 @@
         <v>9</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J13">
         <v>-1</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M13">
         <v>-1</v>
@@ -1482,10 +1482,10 @@
         <v>9</v>
       </c>
       <c r="W13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y13">
         <v>9</v>
@@ -1514,19 +1514,19 @@
         <v>10</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J14">
         <v>-1</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M14">
         <v>-1</v>
@@ -1591,19 +1591,19 @@
         <v>9</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J15">
         <v>-1</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M15">
         <v>-1</v>
@@ -1627,7 +1627,7 @@
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U15">
         <v>9</v>
@@ -1668,19 +1668,19 @@
         <v>9</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J16">
         <v>-1</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M16">
         <v>-1</v>
@@ -1704,7 +1704,7 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U16">
         <v>8</v>
@@ -1716,7 +1716,7 @@
         <v>8</v>
       </c>
       <c r="X16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y16">
         <v>9</v>
@@ -1745,19 +1745,19 @@
         <v>9</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J17">
         <v>-1</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M17">
         <v>-1</v>
@@ -1784,13 +1784,13 @@
         <v>7</v>
       </c>
       <c r="U17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V17">
         <v>7</v>
       </c>
       <c r="W17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X17">
         <v>8</v>
@@ -1822,19 +1822,19 @@
         <v>8</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J18">
         <v>-1</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M18">
         <v>-1</v>
@@ -1861,16 +1861,16 @@
         <v>9</v>
       </c>
       <c r="U18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V18">
         <v>6</v>
       </c>
       <c r="W18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y18">
         <v>8</v>
@@ -1899,19 +1899,19 @@
         <v>9</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J19">
         <v>-1</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M19">
         <v>-1</v>
@@ -1938,13 +1938,13 @@
         <v>7</v>
       </c>
       <c r="U19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V19">
         <v>5</v>
       </c>
       <c r="W19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X19">
         <v>9</v>
@@ -1976,19 +1976,19 @@
         <v>9</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J20">
         <v>-1</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M20">
         <v>-1</v>
@@ -2012,19 +2012,19 @@
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V20">
         <v>7</v>
       </c>
       <c r="W20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y20">
         <v>9</v>
@@ -2053,19 +2053,19 @@
         <v>9</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J21">
         <v>-1</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M21">
         <v>-1</v>
@@ -2089,7 +2089,7 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U21">
         <v>9</v>
@@ -2101,7 +2101,7 @@
         <v>7</v>
       </c>
       <c r="X21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y21">
         <v>9</v>
@@ -2130,19 +2130,19 @@
         <v>9</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J22">
         <v>-1</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M22">
         <v>-1</v>
@@ -2207,19 +2207,19 @@
         <v>7</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J23">
         <v>-1</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M23">
         <v>-1</v>
@@ -2255,7 +2255,7 @@
         <v>6</v>
       </c>
       <c r="X23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y23">
         <v>7</v>
@@ -2284,19 +2284,19 @@
         <v>10</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J24">
         <v>-1</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M24">
         <v>-1</v>
@@ -2320,10 +2320,10 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V24">
         <v>9</v>
@@ -2332,7 +2332,7 @@
         <v>8</v>
       </c>
       <c r="X24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y24">
         <v>10</v>
@@ -2361,19 +2361,19 @@
         <v>10</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J25">
         <v>-1</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M25">
         <v>-1</v>
@@ -2409,7 +2409,7 @@
         <v>9</v>
       </c>
       <c r="X25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y25">
         <v>10</v>
@@ -2438,19 +2438,19 @@
         <v>9</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J26">
         <v>-1</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M26">
         <v>-1</v>
@@ -2515,19 +2515,19 @@
         <v>10</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J27">
         <v>-1</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M27">
         <v>-1</v>
@@ -2551,19 +2551,19 @@
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U27">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V27">
         <v>6</v>
       </c>
       <c r="W27">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X27">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y27">
         <v>10</v>
@@ -2592,19 +2592,19 @@
         <v>10</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J28">
         <v>-1</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M28">
         <v>-1</v>
@@ -2669,19 +2669,19 @@
         <v>10</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J29">
         <v>-1</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M29">
         <v>-1</v>
@@ -2714,7 +2714,7 @@
         <v>7</v>
       </c>
       <c r="W29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X29">
         <v>7</v>
@@ -2746,19 +2746,19 @@
         <v>10</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J30">
         <v>-1</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M30">
         <v>-1</v>
@@ -2782,7 +2782,7 @@
         <v>-1</v>
       </c>
       <c r="T30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U30">
         <v>9</v>
@@ -2791,7 +2791,7 @@
         <v>7</v>
       </c>
       <c r="W30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X30">
         <v>8</v>
@@ -2823,19 +2823,19 @@
         <v>10</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J31">
         <v>-1</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M31">
         <v>-1</v>
@@ -2859,7 +2859,7 @@
         <v>-1</v>
       </c>
       <c r="T31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U31">
         <v>8</v>
@@ -2900,19 +2900,19 @@
         <v>6</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J32">
         <v>-1</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M32">
         <v>-1</v>
@@ -2936,10 +2936,10 @@
         <v>-1</v>
       </c>
       <c r="T32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V32">
         <v>6</v>
@@ -2948,7 +2948,7 @@
         <v>5</v>
       </c>
       <c r="X32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y32">
         <v>6</v>
@@ -2977,19 +2977,19 @@
         <v>10</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J33">
         <v>-1</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M33">
         <v>-1</v>
@@ -3022,7 +3022,7 @@
         <v>9</v>
       </c>
       <c r="W33">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X33">
         <v>10</v>
@@ -3176,7 +3176,7 @@
         <v>100</v>
       </c>
       <c r="L4">
-        <v>97.09999999999999</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="M4">
         <v>100</v>
@@ -3194,7 +3194,7 @@
         <v>100</v>
       </c>
       <c r="R4">
-        <v>97.09999999999999</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="S4">
         <v>100</v>
@@ -3232,10 +3232,10 @@
         <v>93.8</v>
       </c>
       <c r="K5">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="L5">
-        <v>94.3</v>
+        <v>95.7</v>
       </c>
       <c r="M5">
         <v>81</v>
@@ -3250,10 +3250,10 @@
         <v>93.8</v>
       </c>
       <c r="Q5">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="R5">
-        <v>94.3</v>
+        <v>95.7</v>
       </c>
       <c r="S5">
         <v>81</v>
@@ -3294,7 +3294,7 @@
         <v>100</v>
       </c>
       <c r="L6">
-        <v>97.09999999999999</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="M6">
         <v>95.2</v>
@@ -3312,7 +3312,7 @@
         <v>100</v>
       </c>
       <c r="R6">
-        <v>97.09999999999999</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="S6">
         <v>95.2</v>
@@ -3409,10 +3409,10 @@
         <v>100</v>
       </c>
       <c r="K8">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L8">
-        <v>91.40000000000001</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="M8">
         <v>90.5</v>
@@ -3427,10 +3427,10 @@
         <v>100</v>
       </c>
       <c r="Q8">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="R8">
-        <v>91.40000000000001</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="S8">
         <v>90.5</v>
@@ -3471,7 +3471,7 @@
         <v>100</v>
       </c>
       <c r="L9">
-        <v>94.3</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="M9">
         <v>100</v>
@@ -3489,7 +3489,7 @@
         <v>100</v>
       </c>
       <c r="R9">
-        <v>94.3</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="S9">
         <v>100</v>
@@ -3530,7 +3530,7 @@
         <v>100</v>
       </c>
       <c r="L10">
-        <v>97.09999999999999</v>
+        <v>95.7</v>
       </c>
       <c r="M10">
         <v>100</v>
@@ -3548,7 +3548,7 @@
         <v>100</v>
       </c>
       <c r="R10">
-        <v>97.09999999999999</v>
+        <v>95.7</v>
       </c>
       <c r="S10">
         <v>100</v>
@@ -3589,7 +3589,7 @@
         <v>100</v>
       </c>
       <c r="L11">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="M11">
         <v>100</v>
@@ -3607,7 +3607,7 @@
         <v>100</v>
       </c>
       <c r="R11">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="S11">
         <v>100</v>
@@ -3639,7 +3639,7 @@
         <v>100</v>
       </c>
       <c r="I12">
-        <v>95.8</v>
+        <v>97.8</v>
       </c>
       <c r="J12">
         <v>100</v>
@@ -3648,7 +3648,7 @@
         <v>100</v>
       </c>
       <c r="L12">
-        <v>100</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="M12">
         <v>100</v>
@@ -3657,7 +3657,7 @@
         <v>100</v>
       </c>
       <c r="O12">
-        <v>95.8</v>
+        <v>97.8</v>
       </c>
       <c r="P12">
         <v>100</v>
@@ -3666,7 +3666,7 @@
         <v>100</v>
       </c>
       <c r="R12">
-        <v>100</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="S12">
         <v>100</v>
@@ -3763,10 +3763,10 @@
         <v>100</v>
       </c>
       <c r="K14">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L14">
-        <v>97.09999999999999</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="M14">
         <v>100</v>
@@ -3781,10 +3781,10 @@
         <v>100</v>
       </c>
       <c r="Q14">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="R14">
-        <v>97.09999999999999</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="S14">
         <v>100</v>
@@ -3825,7 +3825,7 @@
         <v>100</v>
       </c>
       <c r="L15">
-        <v>100</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="M15">
         <v>100</v>
@@ -3843,7 +3843,7 @@
         <v>100</v>
       </c>
       <c r="R15">
-        <v>100</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="S15">
         <v>100</v>
@@ -3884,7 +3884,7 @@
         <v>100</v>
       </c>
       <c r="L16">
-        <v>100</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="M16">
         <v>100</v>
@@ -3902,7 +3902,7 @@
         <v>100</v>
       </c>
       <c r="R16">
-        <v>100</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="S16">
         <v>100</v>
@@ -3940,10 +3940,10 @@
         <v>93.8</v>
       </c>
       <c r="K17">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L17">
-        <v>85.7</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="M17">
         <v>100</v>
@@ -3958,10 +3958,10 @@
         <v>93.8</v>
       </c>
       <c r="Q17">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R17">
-        <v>85.7</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="S17">
         <v>100</v>
@@ -3999,10 +3999,10 @@
         <v>100</v>
       </c>
       <c r="K18">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L18">
-        <v>97.09999999999999</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="M18">
         <v>100</v>
@@ -4017,10 +4017,10 @@
         <v>100</v>
       </c>
       <c r="Q18">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R18">
-        <v>97.09999999999999</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="S18">
         <v>100</v>
@@ -4052,7 +4052,7 @@
         <v>100</v>
       </c>
       <c r="I19">
-        <v>100</v>
+        <v>97.8</v>
       </c>
       <c r="J19">
         <v>93.8</v>
@@ -4061,7 +4061,7 @@
         <v>100</v>
       </c>
       <c r="L19">
-        <v>94.3</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="M19">
         <v>100</v>
@@ -4070,7 +4070,7 @@
         <v>100</v>
       </c>
       <c r="O19">
-        <v>100</v>
+        <v>97.8</v>
       </c>
       <c r="P19">
         <v>93.8</v>
@@ -4079,7 +4079,7 @@
         <v>100</v>
       </c>
       <c r="R19">
-        <v>94.3</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="S19">
         <v>100</v>
@@ -4111,7 +4111,7 @@
         <v>100</v>
       </c>
       <c r="I20">
-        <v>95.8</v>
+        <v>97.8</v>
       </c>
       <c r="J20">
         <v>100</v>
@@ -4129,7 +4129,7 @@
         <v>100</v>
       </c>
       <c r="O20">
-        <v>95.8</v>
+        <v>97.8</v>
       </c>
       <c r="P20">
         <v>100</v>
@@ -4179,7 +4179,7 @@
         <v>100</v>
       </c>
       <c r="L21">
-        <v>97.09999999999999</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="M21">
         <v>100</v>
@@ -4197,7 +4197,7 @@
         <v>100</v>
       </c>
       <c r="R21">
-        <v>97.09999999999999</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="S21">
         <v>100</v>
@@ -4229,7 +4229,7 @@
         <v>100</v>
       </c>
       <c r="I22">
-        <v>100</v>
+        <v>97.8</v>
       </c>
       <c r="J22">
         <v>93.8</v>
@@ -4238,7 +4238,7 @@
         <v>100</v>
       </c>
       <c r="L22">
-        <v>100</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="M22">
         <v>100</v>
@@ -4247,7 +4247,7 @@
         <v>100</v>
       </c>
       <c r="O22">
-        <v>100</v>
+        <v>97.8</v>
       </c>
       <c r="P22">
         <v>93.8</v>
@@ -4256,7 +4256,7 @@
         <v>100</v>
       </c>
       <c r="R22">
-        <v>100</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="S22">
         <v>100</v>
@@ -4294,10 +4294,10 @@
         <v>100</v>
       </c>
       <c r="K23">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L23">
-        <v>97.09999999999999</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="M23">
         <v>100</v>
@@ -4312,10 +4312,10 @@
         <v>100</v>
       </c>
       <c r="Q23">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R23">
-        <v>97.09999999999999</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="S23">
         <v>100</v>
@@ -4533,7 +4533,7 @@
         <v>96</v>
       </c>
       <c r="L27">
-        <v>97.09999999999999</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="M27">
         <v>100</v>
@@ -4551,7 +4551,7 @@
         <v>96</v>
       </c>
       <c r="R27">
-        <v>97.09999999999999</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="S27">
         <v>100</v>
@@ -4651,7 +4651,7 @@
         <v>100</v>
       </c>
       <c r="L29">
-        <v>100</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="M29">
         <v>100</v>
@@ -4669,7 +4669,7 @@
         <v>100</v>
       </c>
       <c r="R29">
-        <v>100</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="S29">
         <v>100</v>
@@ -4710,7 +4710,7 @@
         <v>100</v>
       </c>
       <c r="L30">
-        <v>100</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="M30">
         <v>100</v>
@@ -4728,7 +4728,7 @@
         <v>100</v>
       </c>
       <c r="R30">
-        <v>100</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="S30">
         <v>100</v>
@@ -4819,16 +4819,16 @@
         <v>100</v>
       </c>
       <c r="I32">
-        <v>95.8</v>
+        <v>97.8</v>
       </c>
       <c r="J32">
         <v>87.5</v>
       </c>
       <c r="K32">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L32">
-        <v>94.3</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="M32">
         <v>85.7</v>
@@ -4837,16 +4837,16 @@
         <v>100</v>
       </c>
       <c r="O32">
-        <v>95.8</v>
+        <v>97.8</v>
       </c>
       <c r="P32">
         <v>87.5</v>
       </c>
       <c r="Q32">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="R32">
-        <v>94.3</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="S32">
         <v>85.7</v>
@@ -4887,7 +4887,7 @@
         <v>100</v>
       </c>
       <c r="L33">
-        <v>97.09999999999999</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="M33">
         <v>100</v>
@@ -4905,7 +4905,7 @@
         <v>100</v>
       </c>
       <c r="R33">
-        <v>97.09999999999999</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="S33">
         <v>100</v>
@@ -5082,7 +5082,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5114,7 +5114,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>8.5</v>
+        <v>8.9</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5146,7 +5146,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>8.4</v>
+        <v>8.9</v>
       </c>
       <c r="I7">
         <v>0</v>

--- a/grupos/3ASV - Estadisticos 20231.xlsx
+++ b/grupos/3ASV - Estadisticos 20231.xlsx
@@ -750,7 +750,7 @@
         <v>9</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K4">
         <v>7</v>
@@ -759,7 +759,7 @@
         <v>10</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -827,7 +827,7 @@
         <v>8</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K5">
         <v>5</v>
@@ -836,7 +836,7 @@
         <v>6</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -904,7 +904,7 @@
         <v>9</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K6">
         <v>7</v>
@@ -913,7 +913,7 @@
         <v>10</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -981,7 +981,7 @@
         <v>8</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K7">
         <v>8</v>
@@ -990,7 +990,7 @@
         <v>10</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1017,7 +1017,7 @@
         <v>9</v>
       </c>
       <c r="V7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W7">
         <v>8</v>
@@ -1026,7 +1026,7 @@
         <v>10</v>
       </c>
       <c r="Y7">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1058,7 +1058,7 @@
         <v>9</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K8">
         <v>8</v>
@@ -1067,7 +1067,7 @@
         <v>10</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1094,7 +1094,7 @@
         <v>9</v>
       </c>
       <c r="V8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W8">
         <v>8</v>
@@ -1103,7 +1103,7 @@
         <v>9</v>
       </c>
       <c r="Y8">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1135,7 +1135,7 @@
         <v>8</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K9">
         <v>8</v>
@@ -1144,7 +1144,7 @@
         <v>10</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1180,7 +1180,7 @@
         <v>10</v>
       </c>
       <c r="Y9">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1212,7 +1212,7 @@
         <v>7</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K10">
         <v>8</v>
@@ -1221,7 +1221,7 @@
         <v>8</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1248,7 +1248,7 @@
         <v>7</v>
       </c>
       <c r="V10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W10">
         <v>8</v>
@@ -1257,7 +1257,7 @@
         <v>9</v>
       </c>
       <c r="Y10">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1289,7 +1289,7 @@
         <v>8</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K11">
         <v>6</v>
@@ -1298,7 +1298,7 @@
         <v>9</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1325,7 +1325,7 @@
         <v>9</v>
       </c>
       <c r="V11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W11">
         <v>7</v>
@@ -1334,7 +1334,7 @@
         <v>10</v>
       </c>
       <c r="Y11">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1366,7 +1366,7 @@
         <v>8</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K12">
         <v>8</v>
@@ -1375,7 +1375,7 @@
         <v>10</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1402,7 +1402,7 @@
         <v>9</v>
       </c>
       <c r="V12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W12">
         <v>8</v>
@@ -1443,7 +1443,7 @@
         <v>9</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K13">
         <v>9</v>
@@ -1452,7 +1452,7 @@
         <v>10</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1520,7 +1520,7 @@
         <v>10</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K14">
         <v>8</v>
@@ -1529,7 +1529,7 @@
         <v>10</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1597,7 +1597,7 @@
         <v>8</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K15">
         <v>9</v>
@@ -1606,7 +1606,7 @@
         <v>10</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1674,7 +1674,7 @@
         <v>8</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K16">
         <v>8</v>
@@ -1683,7 +1683,7 @@
         <v>9</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1751,7 +1751,7 @@
         <v>7</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K17">
         <v>5</v>
@@ -1760,7 +1760,7 @@
         <v>8</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -1796,7 +1796,7 @@
         <v>8</v>
       </c>
       <c r="Y17">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -1828,7 +1828,7 @@
         <v>8</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K18">
         <v>7</v>
@@ -1837,7 +1837,7 @@
         <v>9</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -1864,7 +1864,7 @@
         <v>8</v>
       </c>
       <c r="V18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W18">
         <v>7</v>
@@ -1873,7 +1873,7 @@
         <v>9</v>
       </c>
       <c r="Y18">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -1905,7 +1905,7 @@
         <v>7</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K19">
         <v>7</v>
@@ -1914,7 +1914,7 @@
         <v>8</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -1950,7 +1950,7 @@
         <v>9</v>
       </c>
       <c r="Y19">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -1982,7 +1982,7 @@
         <v>7</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K20">
         <v>7</v>
@@ -1991,7 +1991,7 @@
         <v>6</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2018,7 +2018,7 @@
         <v>8</v>
       </c>
       <c r="V20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W20">
         <v>7</v>
@@ -2027,7 +2027,7 @@
         <v>7</v>
       </c>
       <c r="Y20">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2059,7 +2059,7 @@
         <v>8</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K21">
         <v>7</v>
@@ -2068,7 +2068,7 @@
         <v>10</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2095,7 +2095,7 @@
         <v>9</v>
       </c>
       <c r="V21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W21">
         <v>7</v>
@@ -2104,7 +2104,7 @@
         <v>9</v>
       </c>
       <c r="Y21">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2136,7 +2136,7 @@
         <v>7</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K22">
         <v>8</v>
@@ -2145,7 +2145,7 @@
         <v>10</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2172,7 +2172,7 @@
         <v>7</v>
       </c>
       <c r="V22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W22">
         <v>8</v>
@@ -2181,7 +2181,7 @@
         <v>10</v>
       </c>
       <c r="Y22">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2213,7 +2213,7 @@
         <v>7</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K23">
         <v>6</v>
@@ -2222,7 +2222,7 @@
         <v>7</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2249,7 +2249,7 @@
         <v>8</v>
       </c>
       <c r="V23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W23">
         <v>6</v>
@@ -2290,7 +2290,7 @@
         <v>10</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K24">
         <v>8</v>
@@ -2299,7 +2299,7 @@
         <v>10</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2335,7 +2335,7 @@
         <v>10</v>
       </c>
       <c r="Y24">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2367,7 +2367,7 @@
         <v>9</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K25">
         <v>8</v>
@@ -2376,7 +2376,7 @@
         <v>10</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2403,7 +2403,7 @@
         <v>10</v>
       </c>
       <c r="V25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W25">
         <v>9</v>
@@ -2444,7 +2444,7 @@
         <v>10</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K26">
         <v>8</v>
@@ -2453,7 +2453,7 @@
         <v>8</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2480,7 +2480,7 @@
         <v>10</v>
       </c>
       <c r="V26">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W26">
         <v>8</v>
@@ -2489,7 +2489,7 @@
         <v>9</v>
       </c>
       <c r="Y26">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2521,7 +2521,7 @@
         <v>6</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K27">
         <v>6</v>
@@ -2530,7 +2530,7 @@
         <v>9</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2566,7 +2566,7 @@
         <v>8</v>
       </c>
       <c r="Y27">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2598,7 +2598,7 @@
         <v>10</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K28">
         <v>9</v>
@@ -2607,7 +2607,7 @@
         <v>10</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2634,7 +2634,7 @@
         <v>10</v>
       </c>
       <c r="V28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W28">
         <v>9</v>
@@ -2675,7 +2675,7 @@
         <v>9</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K29">
         <v>9</v>
@@ -2684,7 +2684,7 @@
         <v>7</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -2711,7 +2711,7 @@
         <v>10</v>
       </c>
       <c r="V29">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W29">
         <v>9</v>
@@ -2720,7 +2720,7 @@
         <v>7</v>
       </c>
       <c r="Y29">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2752,7 +2752,7 @@
         <v>9</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K30">
         <v>6</v>
@@ -2761,7 +2761,7 @@
         <v>8</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -2788,7 +2788,7 @@
         <v>9</v>
       </c>
       <c r="V30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W30">
         <v>7</v>
@@ -2797,7 +2797,7 @@
         <v>8</v>
       </c>
       <c r="Y30">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -2829,7 +2829,7 @@
         <v>8</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K31">
         <v>6</v>
@@ -2838,7 +2838,7 @@
         <v>10</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -2865,7 +2865,7 @@
         <v>8</v>
       </c>
       <c r="V31">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W31">
         <v>7</v>
@@ -2874,7 +2874,7 @@
         <v>10</v>
       </c>
       <c r="Y31">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -2906,7 +2906,7 @@
         <v>8</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K32">
         <v>6</v>
@@ -2915,7 +2915,7 @@
         <v>8</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -2983,7 +2983,7 @@
         <v>9</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K33">
         <v>9</v>
@@ -2992,7 +2992,7 @@
         <v>9</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -3028,7 +3028,7 @@
         <v>10</v>
       </c>
       <c r="Y33">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -3229,7 +3229,7 @@
         <v>100</v>
       </c>
       <c r="J5">
-        <v>93.8</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="K5">
         <v>93</v>
@@ -3238,7 +3238,7 @@
         <v>95.7</v>
       </c>
       <c r="M5">
-        <v>81</v>
+        <v>90.7</v>
       </c>
       <c r="N5">
         <v>100</v>
@@ -3247,7 +3247,7 @@
         <v>100</v>
       </c>
       <c r="P5">
-        <v>93.8</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Q5">
         <v>93</v>
@@ -3256,7 +3256,7 @@
         <v>95.7</v>
       </c>
       <c r="S5">
-        <v>81</v>
+        <v>90.7</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -3297,7 +3297,7 @@
         <v>98.59999999999999</v>
       </c>
       <c r="M6">
-        <v>95.2</v>
+        <v>97.7</v>
       </c>
       <c r="N6">
         <v>100</v>
@@ -3315,7 +3315,7 @@
         <v>98.59999999999999</v>
       </c>
       <c r="S6">
-        <v>95.2</v>
+        <v>97.7</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -3406,7 +3406,7 @@
         <v>100</v>
       </c>
       <c r="J8">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="K8">
         <v>95</v>
@@ -3415,7 +3415,7 @@
         <v>92.90000000000001</v>
       </c>
       <c r="M8">
-        <v>90.5</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="N8">
         <v>100</v>
@@ -3424,7 +3424,7 @@
         <v>100</v>
       </c>
       <c r="P8">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="Q8">
         <v>95</v>
@@ -3433,7 +3433,7 @@
         <v>92.90000000000001</v>
       </c>
       <c r="S8">
-        <v>90.5</v>
+        <v>81.40000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -3474,7 +3474,7 @@
         <v>97.09999999999999</v>
       </c>
       <c r="M9">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="N9">
         <v>100</v>
@@ -3492,7 +3492,7 @@
         <v>97.09999999999999</v>
       </c>
       <c r="S9">
-        <v>100</v>
+        <v>97.7</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -3533,7 +3533,7 @@
         <v>95.7</v>
       </c>
       <c r="M10">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="N10">
         <v>100</v>
@@ -3551,7 +3551,7 @@
         <v>95.7</v>
       </c>
       <c r="S10">
-        <v>100</v>
+        <v>97.7</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -3592,7 +3592,7 @@
         <v>90</v>
       </c>
       <c r="M11">
-        <v>100</v>
+        <v>95.3</v>
       </c>
       <c r="N11">
         <v>100</v>
@@ -3610,7 +3610,7 @@
         <v>90</v>
       </c>
       <c r="S11">
-        <v>100</v>
+        <v>95.3</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -3642,7 +3642,7 @@
         <v>97.8</v>
       </c>
       <c r="J12">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="K12">
         <v>100</v>
@@ -3651,7 +3651,7 @@
         <v>97.09999999999999</v>
       </c>
       <c r="M12">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="N12">
         <v>100</v>
@@ -3660,7 +3660,7 @@
         <v>97.8</v>
       </c>
       <c r="P12">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="Q12">
         <v>100</v>
@@ -3669,7 +3669,7 @@
         <v>97.09999999999999</v>
       </c>
       <c r="S12">
-        <v>100</v>
+        <v>97.7</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -3710,7 +3710,7 @@
         <v>100</v>
       </c>
       <c r="M13">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="N13">
         <v>100</v>
@@ -3728,7 +3728,7 @@
         <v>100</v>
       </c>
       <c r="S13">
-        <v>100</v>
+        <v>97.7</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -3760,7 +3760,7 @@
         <v>100</v>
       </c>
       <c r="J14">
-        <v>100</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="K14">
         <v>98</v>
@@ -3769,7 +3769,7 @@
         <v>92.90000000000001</v>
       </c>
       <c r="M14">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="N14">
         <v>100</v>
@@ -3778,7 +3778,7 @@
         <v>100</v>
       </c>
       <c r="P14">
-        <v>100</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Q14">
         <v>98</v>
@@ -3787,7 +3787,7 @@
         <v>92.90000000000001</v>
       </c>
       <c r="S14">
-        <v>100</v>
+        <v>97.7</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -3887,7 +3887,7 @@
         <v>97.09999999999999</v>
       </c>
       <c r="M16">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="N16">
         <v>100</v>
@@ -3905,7 +3905,7 @@
         <v>97.09999999999999</v>
       </c>
       <c r="S16">
-        <v>100</v>
+        <v>97.7</v>
       </c>
     </row>
     <row r="17" spans="1:19">
@@ -3946,7 +3946,7 @@
         <v>82.90000000000001</v>
       </c>
       <c r="M17">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="N17">
         <v>100</v>
@@ -3964,7 +3964,7 @@
         <v>82.90000000000001</v>
       </c>
       <c r="S17">
-        <v>100</v>
+        <v>97.7</v>
       </c>
     </row>
     <row r="18" spans="1:19">
@@ -4114,7 +4114,7 @@
         <v>97.8</v>
       </c>
       <c r="J20">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="K20">
         <v>100</v>
@@ -4123,7 +4123,7 @@
         <v>100</v>
       </c>
       <c r="M20">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="N20">
         <v>100</v>
@@ -4132,7 +4132,7 @@
         <v>97.8</v>
       </c>
       <c r="P20">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q20">
         <v>100</v>
@@ -4141,7 +4141,7 @@
         <v>100</v>
       </c>
       <c r="S20">
-        <v>100</v>
+        <v>97.7</v>
       </c>
     </row>
     <row r="21" spans="1:19">
@@ -4173,7 +4173,7 @@
         <v>100</v>
       </c>
       <c r="J21">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="K21">
         <v>100</v>
@@ -4191,7 +4191,7 @@
         <v>100</v>
       </c>
       <c r="P21">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q21">
         <v>100</v>
@@ -4291,7 +4291,7 @@
         <v>100</v>
       </c>
       <c r="J23">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="K23">
         <v>98</v>
@@ -4300,7 +4300,7 @@
         <v>98.59999999999999</v>
       </c>
       <c r="M23">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="N23">
         <v>100</v>
@@ -4309,7 +4309,7 @@
         <v>100</v>
       </c>
       <c r="P23">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q23">
         <v>98</v>
@@ -4318,7 +4318,7 @@
         <v>98.59999999999999</v>
       </c>
       <c r="S23">
-        <v>100</v>
+        <v>97.7</v>
       </c>
     </row>
     <row r="24" spans="1:19">
@@ -4418,7 +4418,7 @@
         <v>100</v>
       </c>
       <c r="M25">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="N25">
         <v>100</v>
@@ -4436,7 +4436,7 @@
         <v>100</v>
       </c>
       <c r="S25">
-        <v>100</v>
+        <v>97.7</v>
       </c>
     </row>
     <row r="26" spans="1:19">
@@ -4477,7 +4477,7 @@
         <v>97.09999999999999</v>
       </c>
       <c r="M26">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="N26">
         <v>100</v>
@@ -4495,7 +4495,7 @@
         <v>97.09999999999999</v>
       </c>
       <c r="S26">
-        <v>100</v>
+        <v>97.7</v>
       </c>
     </row>
     <row r="27" spans="1:19">
@@ -4527,7 +4527,7 @@
         <v>100</v>
       </c>
       <c r="J27">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="K27">
         <v>96</v>
@@ -4536,7 +4536,7 @@
         <v>98.59999999999999</v>
       </c>
       <c r="M27">
-        <v>100</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="N27">
         <v>100</v>
@@ -4545,7 +4545,7 @@
         <v>100</v>
       </c>
       <c r="P27">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q27">
         <v>96</v>
@@ -4554,7 +4554,7 @@
         <v>98.59999999999999</v>
       </c>
       <c r="S27">
-        <v>100</v>
+        <v>88.40000000000001</v>
       </c>
     </row>
     <row r="28" spans="1:19">
@@ -4595,7 +4595,7 @@
         <v>100</v>
       </c>
       <c r="M28">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="N28">
         <v>100</v>
@@ -4613,7 +4613,7 @@
         <v>100</v>
       </c>
       <c r="S28">
-        <v>100</v>
+        <v>97.7</v>
       </c>
     </row>
     <row r="29" spans="1:19">
@@ -4645,7 +4645,7 @@
         <v>100</v>
       </c>
       <c r="J29">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="K29">
         <v>100</v>
@@ -4654,7 +4654,7 @@
         <v>98.59999999999999</v>
       </c>
       <c r="M29">
-        <v>100</v>
+        <v>95.3</v>
       </c>
       <c r="N29">
         <v>100</v>
@@ -4663,7 +4663,7 @@
         <v>100</v>
       </c>
       <c r="P29">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q29">
         <v>100</v>
@@ -4672,7 +4672,7 @@
         <v>98.59999999999999</v>
       </c>
       <c r="S29">
-        <v>100</v>
+        <v>95.3</v>
       </c>
     </row>
     <row r="30" spans="1:19">
@@ -4713,7 +4713,7 @@
         <v>92.90000000000001</v>
       </c>
       <c r="M30">
-        <v>100</v>
+        <v>95.3</v>
       </c>
       <c r="N30">
         <v>100</v>
@@ -4731,7 +4731,7 @@
         <v>92.90000000000001</v>
       </c>
       <c r="S30">
-        <v>100</v>
+        <v>95.3</v>
       </c>
     </row>
     <row r="31" spans="1:19">
@@ -4772,7 +4772,7 @@
         <v>100</v>
       </c>
       <c r="M31">
-        <v>100</v>
+        <v>95.3</v>
       </c>
       <c r="N31">
         <v>100</v>
@@ -4790,7 +4790,7 @@
         <v>100</v>
       </c>
       <c r="S31">
-        <v>100</v>
+        <v>95.3</v>
       </c>
     </row>
     <row r="32" spans="1:19">
@@ -4822,7 +4822,7 @@
         <v>97.8</v>
       </c>
       <c r="J32">
-        <v>87.5</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="K32">
         <v>90</v>
@@ -4831,7 +4831,7 @@
         <v>91.40000000000001</v>
       </c>
       <c r="M32">
-        <v>85.7</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="N32">
         <v>100</v>
@@ -4840,7 +4840,7 @@
         <v>97.8</v>
       </c>
       <c r="P32">
-        <v>87.5</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="Q32">
         <v>90</v>
@@ -4849,7 +4849,7 @@
         <v>91.40000000000001</v>
       </c>
       <c r="S32">
-        <v>85.7</v>
+        <v>81.40000000000001</v>
       </c>
     </row>
     <row r="33" spans="1:19">
@@ -4881,7 +4881,7 @@
         <v>100</v>
       </c>
       <c r="J33">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="K33">
         <v>100</v>
@@ -4890,7 +4890,7 @@
         <v>98.59999999999999</v>
       </c>
       <c r="M33">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="N33">
         <v>100</v>
@@ -4899,7 +4899,7 @@
         <v>100</v>
       </c>
       <c r="P33">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q33">
         <v>100</v>
@@ -4908,7 +4908,7 @@
         <v>98.59999999999999</v>
       </c>
       <c r="S33">
-        <v>100</v>
+        <v>97.7</v>
       </c>
     </row>
   </sheetData>
@@ -4986,7 +4986,7 @@
         <v>6.7</v>
       </c>
       <c r="H2">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -5018,7 +5018,7 @@
         <v>6.7</v>
       </c>
       <c r="H3">
-        <v>8.699999999999999</v>
+        <v>8</v>
       </c>
       <c r="I3">
         <v>0</v>

--- a/grupos/3ASV - Estadisticos 20231.xlsx
+++ b/grupos/3ASV - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="70">
   <si>
     <t>Materia</t>
   </si>
@@ -185,21 +185,21 @@
     <t>Villanueva Morales Luis Arturo</t>
   </si>
   <si>
+    <t>Muñoz Rivadeneyra Salvador</t>
+  </si>
+  <si>
     <t>Hernández Mendoza Delfina</t>
   </si>
   <si>
+    <t>Martínez Castillo Columba</t>
+  </si>
+  <si>
+    <t>Acevedo Rendón Ismael Arturo</t>
+  </si>
+  <si>
     <t>Rodriguez Roman Marisol</t>
   </si>
   <si>
-    <t>Muñoz Rivadeneyra Salvador</t>
-  </si>
-  <si>
-    <t>Martínez Castillo Columba</t>
-  </si>
-  <si>
-    <t>Acevedo Rendón Ismael Arturo</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -212,31 +212,22 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>ELIZALDE</t>
+    <t>BAUTISTA</t>
   </si>
   <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>MORALES</t>
+    <t>ALVAREZ</t>
   </si>
   <si>
     <t>MARTINEZ</t>
   </si>
   <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>JOSE CARMELO</t>
+    <t>EFRAIN DE JESUS</t>
   </si>
   <si>
     <t>GAMALIEL</t>
-  </si>
-  <si>
-    <t>GUILLERMO ALEXANDER</t>
   </si>
 </sst>
 </file>
@@ -762,22 +753,22 @@
         <v>6</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P4">
         <v>-1</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T4">
         <v>9</v>
@@ -795,7 +786,7 @@
         <v>9</v>
       </c>
       <c r="Y4">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -839,40 +830,40 @@
         <v>5</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P5">
         <v>-1</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T5">
         <v>7</v>
       </c>
       <c r="U5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V5">
         <v>5</v>
       </c>
       <c r="W5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y5">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -916,22 +907,22 @@
         <v>8</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P6">
         <v>-1</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T6">
         <v>10</v>
@@ -949,7 +940,7 @@
         <v>9</v>
       </c>
       <c r="Y6">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -993,37 +984,37 @@
         <v>8</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P7">
         <v>-1</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T7">
         <v>10</v>
       </c>
       <c r="U7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V7">
         <v>7</v>
       </c>
       <c r="W7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y7">
         <v>9</v>
@@ -1070,22 +1061,22 @@
         <v>5</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P8">
         <v>-1</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T8">
         <v>10</v>
@@ -1147,25 +1138,25 @@
         <v>6</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P9">
         <v>-1</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U9">
         <v>9</v>
@@ -1224,22 +1215,22 @@
         <v>7</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P10">
         <v>-1</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T10">
         <v>9</v>
@@ -1251,13 +1242,13 @@
         <v>7</v>
       </c>
       <c r="W10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X10">
         <v>9</v>
       </c>
       <c r="Y10">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1301,40 +1292,40 @@
         <v>6</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P11">
         <v>-1</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V11">
         <v>8</v>
       </c>
       <c r="W11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y11">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1378,28 +1369,28 @@
         <v>5</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P12">
         <v>-1</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T12">
         <v>10</v>
       </c>
       <c r="U12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V12">
         <v>6</v>
@@ -1408,10 +1399,10 @@
         <v>8</v>
       </c>
       <c r="X12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y12">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1455,25 +1446,25 @@
         <v>9</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P13">
         <v>-1</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U13">
         <v>10</v>
@@ -1532,22 +1523,22 @@
         <v>9</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P14">
         <v>-1</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T14">
         <v>9</v>
@@ -1609,22 +1600,22 @@
         <v>8</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P15">
         <v>-1</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T15">
         <v>10</v>
@@ -1686,28 +1677,28 @@
         <v>8</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P16">
         <v>-1</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V16">
         <v>8</v>
@@ -1763,22 +1754,22 @@
         <v>6</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P17">
         <v>-1</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T17">
         <v>7</v>
@@ -1790,7 +1781,7 @@
         <v>7</v>
       </c>
       <c r="W17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X17">
         <v>8</v>
@@ -1840,22 +1831,22 @@
         <v>6</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P18">
         <v>-1</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T18">
         <v>9</v>
@@ -1870,10 +1861,10 @@
         <v>7</v>
       </c>
       <c r="X18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y18">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -1917,25 +1908,25 @@
         <v>7</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P19">
         <v>-1</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U19">
         <v>7</v>
@@ -1994,22 +1985,22 @@
         <v>6</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P20">
         <v>-1</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T20">
         <v>9</v>
@@ -2071,22 +2062,22 @@
         <v>7</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P21">
         <v>-1</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T21">
         <v>10</v>
@@ -2098,13 +2089,13 @@
         <v>8</v>
       </c>
       <c r="W21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X21">
         <v>9</v>
       </c>
       <c r="Y21">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2148,22 +2139,22 @@
         <v>6</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P22">
         <v>-1</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T22">
         <v>9</v>
@@ -2175,7 +2166,7 @@
         <v>7</v>
       </c>
       <c r="W22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X22">
         <v>10</v>
@@ -2225,25 +2216,25 @@
         <v>6</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P23">
         <v>-1</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U23">
         <v>8</v>
@@ -2252,7 +2243,7 @@
         <v>6</v>
       </c>
       <c r="W23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X23">
         <v>7</v>
@@ -2302,22 +2293,22 @@
         <v>7</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P24">
         <v>-1</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T24">
         <v>10</v>
@@ -2332,7 +2323,7 @@
         <v>8</v>
       </c>
       <c r="X24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y24">
         <v>9</v>
@@ -2379,34 +2370,34 @@
         <v>9</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P25">
         <v>-1</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T25">
         <v>10</v>
       </c>
       <c r="U25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V25">
         <v>9</v>
       </c>
       <c r="W25">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X25">
         <v>10</v>
@@ -2456,22 +2447,22 @@
         <v>7</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P26">
         <v>-1</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T26">
         <v>9</v>
@@ -2489,7 +2480,7 @@
         <v>9</v>
       </c>
       <c r="Y26">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2533,25 +2524,25 @@
         <v>6</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P27">
         <v>-1</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T27">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U27">
         <v>7</v>
@@ -2560,13 +2551,13 @@
         <v>6</v>
       </c>
       <c r="W27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X27">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y27">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2610,22 +2601,22 @@
         <v>10</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P28">
         <v>-1</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T28">
         <v>10</v>
@@ -2687,28 +2678,28 @@
         <v>6</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P29">
         <v>-1</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T29">
         <v>9</v>
       </c>
       <c r="U29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V29">
         <v>8</v>
@@ -2717,7 +2708,7 @@
         <v>9</v>
       </c>
       <c r="X29">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y29">
         <v>8</v>
@@ -2764,22 +2755,22 @@
         <v>6</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P30">
         <v>-1</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T30">
         <v>7</v>
@@ -2794,10 +2785,10 @@
         <v>7</v>
       </c>
       <c r="X30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y30">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -2841,22 +2832,22 @@
         <v>6</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P31">
         <v>-1</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T31">
         <v>7</v>
@@ -2871,7 +2862,7 @@
         <v>7</v>
       </c>
       <c r="X31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y31">
         <v>8</v>
@@ -2918,22 +2909,22 @@
         <v>6</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P32">
         <v>-1</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T32">
         <v>7</v>
@@ -2945,13 +2936,13 @@
         <v>6</v>
       </c>
       <c r="W32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X32">
         <v>7</v>
       </c>
       <c r="Y32">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -2995,22 +2986,22 @@
         <v>7</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P33">
         <v>-1</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T33">
         <v>9</v>
@@ -3194,7 +3185,7 @@
         <v>100</v>
       </c>
       <c r="R4">
-        <v>98.59999999999999</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="S4">
         <v>100</v>
@@ -3244,19 +3235,19 @@
         <v>100</v>
       </c>
       <c r="O5">
-        <v>100</v>
+        <v>98.5</v>
       </c>
       <c r="P5">
         <v>90.59999999999999</v>
       </c>
       <c r="Q5">
-        <v>93</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="R5">
-        <v>95.7</v>
+        <v>95.5</v>
       </c>
       <c r="S5">
-        <v>90.7</v>
+        <v>92.2</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -3312,10 +3303,10 @@
         <v>100</v>
       </c>
       <c r="R6">
-        <v>98.59999999999999</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="S6">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -3427,13 +3418,13 @@
         <v>93.8</v>
       </c>
       <c r="Q8">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="R8">
         <v>92.90000000000001</v>
       </c>
       <c r="S8">
-        <v>81.40000000000001</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -3489,10 +3480,10 @@
         <v>100</v>
       </c>
       <c r="R9">
-        <v>97.09999999999999</v>
+        <v>98.2</v>
       </c>
       <c r="S9">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -3548,10 +3539,10 @@
         <v>100</v>
       </c>
       <c r="R10">
-        <v>95.7</v>
+        <v>93.8</v>
       </c>
       <c r="S10">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -3607,10 +3598,10 @@
         <v>100</v>
       </c>
       <c r="R11">
-        <v>90</v>
+        <v>89.3</v>
       </c>
       <c r="S11">
-        <v>95.3</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -3657,7 +3648,7 @@
         <v>100</v>
       </c>
       <c r="O12">
-        <v>97.8</v>
+        <v>97</v>
       </c>
       <c r="P12">
         <v>93.8</v>
@@ -3666,10 +3657,10 @@
         <v>100</v>
       </c>
       <c r="R12">
-        <v>97.09999999999999</v>
+        <v>95.5</v>
       </c>
       <c r="S12">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -3728,7 +3719,7 @@
         <v>100</v>
       </c>
       <c r="S13">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -3781,13 +3772,13 @@
         <v>90.59999999999999</v>
       </c>
       <c r="Q14">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="R14">
         <v>92.90000000000001</v>
       </c>
       <c r="S14">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -3843,7 +3834,7 @@
         <v>100</v>
       </c>
       <c r="R15">
-        <v>97.09999999999999</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="S15">
         <v>100</v>
@@ -3893,7 +3884,7 @@
         <v>100</v>
       </c>
       <c r="O16">
-        <v>100</v>
+        <v>98.5</v>
       </c>
       <c r="P16">
         <v>100</v>
@@ -3902,10 +3893,10 @@
         <v>100</v>
       </c>
       <c r="R16">
-        <v>97.09999999999999</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="S16">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:19">
@@ -3952,19 +3943,19 @@
         <v>100</v>
       </c>
       <c r="O17">
-        <v>100</v>
+        <v>98.5</v>
       </c>
       <c r="P17">
         <v>93.8</v>
       </c>
       <c r="Q17">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="R17">
-        <v>82.90000000000001</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="S17">
-        <v>97.7</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="18" spans="1:19">
@@ -4017,7 +4008,7 @@
         <v>100</v>
       </c>
       <c r="Q18">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="R18">
         <v>92.90000000000001</v>
@@ -4070,7 +4061,7 @@
         <v>100</v>
       </c>
       <c r="O19">
-        <v>97.8</v>
+        <v>95.5</v>
       </c>
       <c r="P19">
         <v>93.8</v>
@@ -4079,7 +4070,7 @@
         <v>100</v>
       </c>
       <c r="R19">
-        <v>97.09999999999999</v>
+        <v>98.2</v>
       </c>
       <c r="S19">
         <v>100</v>
@@ -4129,19 +4120,19 @@
         <v>100</v>
       </c>
       <c r="O20">
-        <v>97.8</v>
+        <v>98.5</v>
       </c>
       <c r="P20">
         <v>96.90000000000001</v>
       </c>
       <c r="Q20">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="R20">
-        <v>100</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="S20">
-        <v>97.7</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="21" spans="1:19">
@@ -4197,7 +4188,7 @@
         <v>100</v>
       </c>
       <c r="R21">
-        <v>98.59999999999999</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="S21">
         <v>100</v>
@@ -4247,7 +4238,7 @@
         <v>100</v>
       </c>
       <c r="O22">
-        <v>97.8</v>
+        <v>97</v>
       </c>
       <c r="P22">
         <v>93.8</v>
@@ -4256,7 +4247,7 @@
         <v>100</v>
       </c>
       <c r="R22">
-        <v>98.59999999999999</v>
+        <v>98.2</v>
       </c>
       <c r="S22">
         <v>100</v>
@@ -4312,13 +4303,13 @@
         <v>96.90000000000001</v>
       </c>
       <c r="Q23">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="R23">
-        <v>98.59999999999999</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="S23">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="24" spans="1:19">
@@ -4436,7 +4427,7 @@
         <v>100</v>
       </c>
       <c r="S25">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="26" spans="1:19">
@@ -4492,10 +4483,10 @@
         <v>100</v>
       </c>
       <c r="R26">
-        <v>97.09999999999999</v>
+        <v>97.3</v>
       </c>
       <c r="S26">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="27" spans="1:19">
@@ -4548,13 +4539,13 @@
         <v>96.90000000000001</v>
       </c>
       <c r="Q27">
-        <v>96</v>
+        <v>97.5</v>
       </c>
       <c r="R27">
-        <v>98.59999999999999</v>
+        <v>98.2</v>
       </c>
       <c r="S27">
-        <v>88.40000000000001</v>
+        <v>92.2</v>
       </c>
     </row>
     <row r="28" spans="1:19">
@@ -4613,7 +4604,7 @@
         <v>100</v>
       </c>
       <c r="S28">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="29" spans="1:19">
@@ -4669,10 +4660,10 @@
         <v>100</v>
       </c>
       <c r="R29">
-        <v>98.59999999999999</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="S29">
-        <v>95.3</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="30" spans="1:19">
@@ -4728,10 +4719,10 @@
         <v>100</v>
       </c>
       <c r="R30">
-        <v>92.90000000000001</v>
+        <v>92</v>
       </c>
       <c r="S30">
-        <v>95.3</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="31" spans="1:19">
@@ -4787,10 +4778,10 @@
         <v>100</v>
       </c>
       <c r="R31">
-        <v>100</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="S31">
-        <v>95.3</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="32" spans="1:19">
@@ -4837,19 +4828,19 @@
         <v>100</v>
       </c>
       <c r="O32">
-        <v>97.8</v>
+        <v>98.5</v>
       </c>
       <c r="P32">
         <v>84.40000000000001</v>
       </c>
       <c r="Q32">
-        <v>90</v>
+        <v>91.3</v>
       </c>
       <c r="R32">
-        <v>91.40000000000001</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="S32">
-        <v>81.40000000000001</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="33" spans="1:19">
@@ -4905,10 +4896,10 @@
         <v>100</v>
       </c>
       <c r="R33">
-        <v>98.59999999999999</v>
+        <v>98.2</v>
       </c>
       <c r="S33">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -4997,7 +4988,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>55</v>
@@ -5006,19 +4997,19 @@
         <v>30</v>
       </c>
       <c r="D3">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F3" s="2">
-        <v>93.3</v>
+        <v>100</v>
       </c>
       <c r="G3" s="2">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5029,7 +5020,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>56</v>
@@ -5038,19 +5029,19 @@
         <v>30</v>
       </c>
       <c r="D4">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F4" s="2">
-        <v>93.3</v>
+        <v>100</v>
       </c>
       <c r="G4" s="2">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5061,7 +5052,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
         <v>57</v>
@@ -5082,7 +5073,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5093,7 +5084,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>58</v>
@@ -5114,7 +5105,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5125,7 +5116,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
         <v>59</v>
@@ -5146,7 +5137,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>8.9</v>
+        <v>7.9</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -5196,7 +5187,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5228,22 +5219,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920298</v>
+        <v>22330051920291</v>
       </c>
       <c r="B2" t="s">
         <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -5257,10 +5248,10 @@
         <v>65</v>
       </c>
       <c r="C3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
@@ -5269,29 +5260,6 @@
         <v>54</v>
       </c>
       <c r="G3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>22330051920314</v>
-      </c>
-      <c r="B4" t="s">
-        <v>66</v>
-      </c>
-      <c r="C4" t="s">
-        <v>69</v>
-      </c>
-      <c r="D4" t="s">
-        <v>72</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>56</v>
-      </c>
-      <c r="G4">
         <v>5</v>
       </c>
     </row>

--- a/grupos/3ASV - Estadisticos 20231.xlsx
+++ b/grupos/3ASV - Estadisticos 20231.xlsx
@@ -2589,7 +2589,7 @@
         <v>10</v>
       </c>
       <c r="J28">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K28">
         <v>9</v>
@@ -2625,7 +2625,7 @@
         <v>10</v>
       </c>
       <c r="V28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W28">
         <v>9</v>

--- a/grupos/3ASV - Estadisticos 20231.xlsx
+++ b/grupos/3ASV - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="64">
   <si>
     <t>Materia</t>
   </si>
@@ -182,12 +182,12 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Muñoz Rivadeneyra Salvador</t>
+  </si>
+  <si>
     <t>Villanueva Morales Luis Arturo</t>
   </si>
   <si>
-    <t>Muñoz Rivadeneyra Salvador</t>
-  </si>
-  <si>
     <t>Hernández Mendoza Delfina</t>
   </si>
   <si>
@@ -210,24 +210,6 @@
   </si>
   <si>
     <t>Nombres</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>EFRAIN DE JESUS</t>
-  </si>
-  <si>
-    <t>GAMALIEL</t>
   </si>
 </sst>
 </file>
@@ -759,7 +741,7 @@
         <v>9</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q4">
         <v>10</v>
@@ -836,7 +818,7 @@
         <v>5</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q5">
         <v>8</v>
@@ -854,7 +836,7 @@
         <v>7</v>
       </c>
       <c r="V5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W5">
         <v>6</v>
@@ -913,7 +895,7 @@
         <v>10</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q6">
         <v>9</v>
@@ -990,7 +972,7 @@
         <v>8</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q7">
         <v>10</v>
@@ -1067,7 +1049,7 @@
         <v>8</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q8">
         <v>8</v>
@@ -1144,7 +1126,7 @@
         <v>9</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q9">
         <v>9</v>
@@ -1221,7 +1203,7 @@
         <v>7</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q10">
         <v>10</v>
@@ -1298,7 +1280,7 @@
         <v>8</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q11">
         <v>9</v>
@@ -1375,7 +1357,7 @@
         <v>6</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q12">
         <v>8</v>
@@ -1393,7 +1375,7 @@
         <v>8</v>
       </c>
       <c r="V12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W12">
         <v>8</v>
@@ -1452,7 +1434,7 @@
         <v>10</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q13">
         <v>9</v>
@@ -1529,7 +1511,7 @@
         <v>10</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q14">
         <v>10</v>
@@ -1606,7 +1588,7 @@
         <v>9</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q15">
         <v>10</v>
@@ -1683,7 +1665,7 @@
         <v>6</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q16">
         <v>7</v>
@@ -1760,7 +1742,7 @@
         <v>8</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q17">
         <v>8</v>
@@ -1837,7 +1819,7 @@
         <v>9</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q18">
         <v>9</v>
@@ -1855,7 +1837,7 @@
         <v>8</v>
       </c>
       <c r="V18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W18">
         <v>7</v>
@@ -1914,7 +1896,7 @@
         <v>8</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q19">
         <v>8</v>
@@ -1932,7 +1914,7 @@
         <v>7</v>
       </c>
       <c r="V19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W19">
         <v>8</v>
@@ -1991,7 +1973,7 @@
         <v>9</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q20">
         <v>8</v>
@@ -2068,7 +2050,7 @@
         <v>9</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q21">
         <v>9</v>
@@ -2145,7 +2127,7 @@
         <v>8</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q22">
         <v>10</v>
@@ -2222,7 +2204,7 @@
         <v>9</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q23">
         <v>9</v>
@@ -2299,7 +2281,7 @@
         <v>10</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q24">
         <v>9</v>
@@ -2376,7 +2358,7 @@
         <v>8</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q25">
         <v>8</v>
@@ -2453,7 +2435,7 @@
         <v>9</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q26">
         <v>8</v>
@@ -2530,7 +2512,7 @@
         <v>8</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q27">
         <v>9</v>
@@ -2548,7 +2530,7 @@
         <v>7</v>
       </c>
       <c r="V27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W27">
         <v>8</v>
@@ -2607,7 +2589,7 @@
         <v>10</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q28">
         <v>10</v>
@@ -2684,7 +2666,7 @@
         <v>8</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q29">
         <v>9</v>
@@ -2761,7 +2743,7 @@
         <v>9</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q30">
         <v>8</v>
@@ -2838,7 +2820,7 @@
         <v>8</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q31">
         <v>7</v>
@@ -2856,7 +2838,7 @@
         <v>8</v>
       </c>
       <c r="V31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W31">
         <v>7</v>
@@ -2915,7 +2897,7 @@
         <v>10</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q32">
         <v>8</v>
@@ -2933,7 +2915,7 @@
         <v>8</v>
       </c>
       <c r="V32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W32">
         <v>6</v>
@@ -2992,7 +2974,7 @@
         <v>10</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q33">
         <v>9</v>
@@ -3238,7 +3220,7 @@
         <v>98.5</v>
       </c>
       <c r="P5">
-        <v>90.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="Q5">
         <v>94.40000000000001</v>
@@ -3415,7 +3397,7 @@
         <v>100</v>
       </c>
       <c r="P8">
-        <v>93.8</v>
+        <v>95.8</v>
       </c>
       <c r="Q8">
         <v>96.90000000000001</v>
@@ -3651,7 +3633,7 @@
         <v>97</v>
       </c>
       <c r="P12">
-        <v>93.8</v>
+        <v>95.8</v>
       </c>
       <c r="Q12">
         <v>100</v>
@@ -3769,7 +3751,7 @@
         <v>100</v>
       </c>
       <c r="P14">
-        <v>90.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="Q14">
         <v>98.8</v>
@@ -3946,7 +3928,7 @@
         <v>98.5</v>
       </c>
       <c r="P17">
-        <v>93.8</v>
+        <v>95.8</v>
       </c>
       <c r="Q17">
         <v>98.8</v>
@@ -4064,7 +4046,7 @@
         <v>95.5</v>
       </c>
       <c r="P19">
-        <v>93.8</v>
+        <v>95.8</v>
       </c>
       <c r="Q19">
         <v>100</v>
@@ -4123,7 +4105,7 @@
         <v>98.5</v>
       </c>
       <c r="P20">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="Q20">
         <v>98.8</v>
@@ -4182,7 +4164,7 @@
         <v>100</v>
       </c>
       <c r="P21">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="Q21">
         <v>100</v>
@@ -4241,7 +4223,7 @@
         <v>97</v>
       </c>
       <c r="P22">
-        <v>93.8</v>
+        <v>95.8</v>
       </c>
       <c r="Q22">
         <v>100</v>
@@ -4300,7 +4282,7 @@
         <v>100</v>
       </c>
       <c r="P23">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="Q23">
         <v>98.8</v>
@@ -4536,7 +4518,7 @@
         <v>100</v>
       </c>
       <c r="P27">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="Q27">
         <v>97.5</v>
@@ -4654,7 +4636,7 @@
         <v>100</v>
       </c>
       <c r="P29">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="Q29">
         <v>100</v>
@@ -4772,7 +4754,7 @@
         <v>100</v>
       </c>
       <c r="P31">
-        <v>93.8</v>
+        <v>95.8</v>
       </c>
       <c r="Q31">
         <v>100</v>
@@ -4831,7 +4813,7 @@
         <v>98.5</v>
       </c>
       <c r="P32">
-        <v>84.40000000000001</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="Q32">
         <v>91.3</v>
@@ -4890,7 +4872,7 @@
         <v>100</v>
       </c>
       <c r="P33">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="Q33">
         <v>100</v>
@@ -4956,7 +4938,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
         <v>54</v>
@@ -4965,19 +4947,19 @@
         <v>30</v>
       </c>
       <c r="D2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F2" s="2">
-        <v>93.3</v>
+        <v>100</v>
       </c>
       <c r="G2" s="2">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -4988,7 +4970,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
         <v>55</v>
@@ -5009,7 +4991,7 @@
         <v>0</v>
       </c>
       <c r="H3">
-        <v>8.5</v>
+        <v>7.8</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5187,7 +5169,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5217,52 +5199,6 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>22330051920291</v>
-      </c>
-      <c r="B2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D2" t="s">
-        <v>68</v>
-      </c>
-      <c r="E2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" t="s">
-        <v>54</v>
-      </c>
-      <c r="G2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>22330051920305</v>
-      </c>
-      <c r="B3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F3" t="s">
-        <v>54</v>
-      </c>
-      <c r="G3">
-        <v>5</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/grupos/3ASV - Estadisticos 20231.xlsx
+++ b/grupos/3ASV - Estadisticos 20231.xlsx
@@ -753,22 +753,22 @@
         <v>10</v>
       </c>
       <c r="T4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y4">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -830,22 +830,22 @@
         <v>10</v>
       </c>
       <c r="T5">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U5">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V5">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W5">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="X5">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y5">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -910,19 +910,19 @@
         <v>10</v>
       </c>
       <c r="U6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y6">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -987,19 +987,19 @@
         <v>10</v>
       </c>
       <c r="U7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V7">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y7">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1064,19 +1064,19 @@
         <v>10</v>
       </c>
       <c r="U8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V8">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W8">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y8">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1138,22 +1138,22 @@
         <v>10</v>
       </c>
       <c r="T9">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V9">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W9">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X9">
         <v>10</v>
       </c>
       <c r="Y9">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1215,22 +1215,22 @@
         <v>8</v>
       </c>
       <c r="T10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y10">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1292,22 +1292,22 @@
         <v>9</v>
       </c>
       <c r="T11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U11">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V11">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W11">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y11">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1372,19 +1372,19 @@
         <v>10</v>
       </c>
       <c r="U12">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V12">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W12">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X12">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y12">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1446,22 +1446,22 @@
         <v>10</v>
       </c>
       <c r="T13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U13">
         <v>10</v>
       </c>
       <c r="V13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X13">
         <v>10</v>
       </c>
       <c r="Y13">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1523,16 +1523,16 @@
         <v>10</v>
       </c>
       <c r="T14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U14">
         <v>10</v>
       </c>
       <c r="V14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X14">
         <v>10</v>
@@ -1603,19 +1603,19 @@
         <v>10</v>
       </c>
       <c r="U15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X15">
         <v>10</v>
       </c>
       <c r="Y15">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1677,22 +1677,22 @@
         <v>10</v>
       </c>
       <c r="T16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U16">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V16">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W16">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X16">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y16">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1754,22 +1754,22 @@
         <v>8</v>
       </c>
       <c r="T17">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U17">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V17">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W17">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X17">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y17">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -1831,22 +1831,22 @@
         <v>9</v>
       </c>
       <c r="T18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U18">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V18">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W18">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X18">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y18">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -1908,22 +1908,22 @@
         <v>9</v>
       </c>
       <c r="T19">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U19">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V19">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W19">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y19">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -1985,22 +1985,22 @@
         <v>8</v>
       </c>
       <c r="T20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U20">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V20">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W20">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X20">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y20">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2065,19 +2065,19 @@
         <v>10</v>
       </c>
       <c r="U21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V21">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W21">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y21">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2139,22 +2139,22 @@
         <v>8</v>
       </c>
       <c r="T22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U22">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V22">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X22">
         <v>10</v>
       </c>
       <c r="Y22">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2216,22 +2216,22 @@
         <v>8</v>
       </c>
       <c r="T23">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U23">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V23">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W23">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X23">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y23">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2299,16 +2299,16 @@
         <v>10</v>
       </c>
       <c r="V24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W24">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y24">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2373,13 +2373,13 @@
         <v>10</v>
       </c>
       <c r="U25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W25">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X25">
         <v>10</v>
@@ -2447,22 +2447,22 @@
         <v>10</v>
       </c>
       <c r="T26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U26">
         <v>10</v>
       </c>
       <c r="V26">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W26">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y26">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2524,22 +2524,22 @@
         <v>10</v>
       </c>
       <c r="T27">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U27">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V27">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W27">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X27">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y27">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2610,7 +2610,7 @@
         <v>10</v>
       </c>
       <c r="W28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X28">
         <v>10</v>
@@ -2678,22 +2678,22 @@
         <v>9</v>
       </c>
       <c r="T29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V29">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X29">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y29">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2755,22 +2755,22 @@
         <v>10</v>
       </c>
       <c r="T30">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V30">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W30">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y30">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -2832,22 +2832,22 @@
         <v>9</v>
       </c>
       <c r="T31">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U31">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V31">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W31">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y31">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -2909,22 +2909,22 @@
         <v>8</v>
       </c>
       <c r="T32">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U32">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V32">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W32">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="X32">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y32">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -2986,22 +2986,22 @@
         <v>10</v>
       </c>
       <c r="T33">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U33">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V33">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W33">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X33">
         <v>10</v>
       </c>
       <c r="Y33">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -4959,7 +4959,7 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -4991,7 +4991,7 @@
         <v>0</v>
       </c>
       <c r="H3">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5023,7 +5023,7 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5055,7 +5055,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5087,7 +5087,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5119,7 +5119,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>7.9</v>
+        <v>10</v>
       </c>
       <c r="I7">
         <v>0</v>

--- a/grupos/3ASV - Estadisticos 20231.xlsx
+++ b/grupos/3ASV - Estadisticos 20231.xlsx
@@ -753,22 +753,22 @@
         <v>10</v>
       </c>
       <c r="T4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y4">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -830,22 +830,22 @@
         <v>10</v>
       </c>
       <c r="T5">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U5">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V5">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W5">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="X5">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y5">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -910,19 +910,19 @@
         <v>10</v>
       </c>
       <c r="U6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y6">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -987,19 +987,19 @@
         <v>10</v>
       </c>
       <c r="U7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V7">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y7">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1064,19 +1064,19 @@
         <v>10</v>
       </c>
       <c r="U8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V8">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W8">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y8">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1138,22 +1138,22 @@
         <v>10</v>
       </c>
       <c r="T9">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V9">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W9">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X9">
         <v>10</v>
       </c>
       <c r="Y9">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1215,22 +1215,22 @@
         <v>8</v>
       </c>
       <c r="T10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U10">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V10">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y10">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1292,22 +1292,22 @@
         <v>9</v>
       </c>
       <c r="T11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U11">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V11">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W11">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y11">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1372,19 +1372,19 @@
         <v>10</v>
       </c>
       <c r="U12">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V12">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W12">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X12">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y12">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1446,22 +1446,22 @@
         <v>10</v>
       </c>
       <c r="T13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U13">
         <v>10</v>
       </c>
       <c r="V13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X13">
         <v>10</v>
       </c>
       <c r="Y13">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1523,16 +1523,16 @@
         <v>10</v>
       </c>
       <c r="T14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U14">
         <v>10</v>
       </c>
       <c r="V14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X14">
         <v>10</v>
@@ -1603,19 +1603,19 @@
         <v>10</v>
       </c>
       <c r="U15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V15">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X15">
         <v>10</v>
       </c>
       <c r="Y15">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1677,22 +1677,22 @@
         <v>10</v>
       </c>
       <c r="T16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U16">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V16">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W16">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X16">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y16">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1754,22 +1754,22 @@
         <v>8</v>
       </c>
       <c r="T17">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U17">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V17">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W17">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X17">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y17">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -1831,22 +1831,22 @@
         <v>9</v>
       </c>
       <c r="T18">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U18">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V18">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W18">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X18">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y18">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -1908,22 +1908,22 @@
         <v>9</v>
       </c>
       <c r="T19">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U19">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V19">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W19">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y19">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -1985,22 +1985,22 @@
         <v>8</v>
       </c>
       <c r="T20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U20">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V20">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W20">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X20">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y20">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2065,19 +2065,19 @@
         <v>10</v>
       </c>
       <c r="U21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V21">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W21">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y21">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2139,22 +2139,22 @@
         <v>8</v>
       </c>
       <c r="T22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U22">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V22">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X22">
         <v>10</v>
       </c>
       <c r="Y22">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2216,22 +2216,22 @@
         <v>8</v>
       </c>
       <c r="T23">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U23">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V23">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W23">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X23">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y23">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2299,16 +2299,16 @@
         <v>10</v>
       </c>
       <c r="V24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W24">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y24">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2373,13 +2373,13 @@
         <v>10</v>
       </c>
       <c r="U25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W25">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X25">
         <v>10</v>
@@ -2447,22 +2447,22 @@
         <v>10</v>
       </c>
       <c r="T26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U26">
         <v>10</v>
       </c>
       <c r="V26">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W26">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y26">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2524,22 +2524,22 @@
         <v>10</v>
       </c>
       <c r="T27">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U27">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V27">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W27">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X27">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y27">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2610,7 +2610,7 @@
         <v>10</v>
       </c>
       <c r="W28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X28">
         <v>10</v>
@@ -2678,22 +2678,22 @@
         <v>9</v>
       </c>
       <c r="T29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V29">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X29">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y29">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2755,22 +2755,22 @@
         <v>10</v>
       </c>
       <c r="T30">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V30">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W30">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y30">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -2832,22 +2832,22 @@
         <v>9</v>
       </c>
       <c r="T31">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U31">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V31">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W31">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y31">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -2909,22 +2909,22 @@
         <v>8</v>
       </c>
       <c r="T32">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U32">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V32">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W32">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="X32">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y32">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -2986,22 +2986,22 @@
         <v>10</v>
       </c>
       <c r="T33">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U33">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V33">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W33">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X33">
         <v>10</v>
       </c>
       <c r="Y33">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -4959,7 +4959,7 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -4991,7 +4991,7 @@
         <v>0</v>
       </c>
       <c r="H3">
-        <v>10</v>
+        <v>7.8</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5023,7 +5023,7 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5055,7 +5055,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5087,7 +5087,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5119,7 +5119,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>10</v>
+        <v>7.9</v>
       </c>
       <c r="I7">
         <v>0</v>
